--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.8403408051221</v>
+        <v>4.199055380832341</v>
       </c>
       <c r="D2" t="n">
-        <v>11.02192429899469</v>
+        <v>1.791062698586636</v>
       </c>
       <c r="E2" t="n">
-        <v>12.89236382192318</v>
+        <v>2.095009121062516</v>
       </c>
       <c r="F2" t="n">
-        <v>14.06173273605402</v>
+        <v>2.285031569608779</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.47998305415791</v>
+        <v>6.577997246300661</v>
       </c>
       <c r="D3" t="n">
-        <v>40.16464664206272</v>
+        <v>6.526755079335192</v>
       </c>
       <c r="E3" t="n">
-        <v>12.89236382192318</v>
+        <v>2.095009121062516</v>
       </c>
       <c r="F3" t="n">
-        <v>14.06173273605402</v>
+        <v>2.285031569608779</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.06105684893582</v>
+        <v>4.722421737952071</v>
       </c>
       <c r="D4" t="n">
-        <v>28.92696868929368</v>
+        <v>4.700632412010223</v>
       </c>
       <c r="E4" t="n">
-        <v>12.89236382192318</v>
+        <v>2.095009121062516</v>
       </c>
       <c r="F4" t="n">
-        <v>14.06173273605402</v>
+        <v>2.285031569608779</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4.800193288292872</v>
+        <v>0.7800314093475916</v>
       </c>
       <c r="D5" t="n">
-        <v>4.829985715246302</v>
+        <v>0.7848726787275241</v>
       </c>
       <c r="E5" t="n">
-        <v>12.89236382192318</v>
+        <v>2.095009121062516</v>
       </c>
       <c r="F5" t="n">
-        <v>14.06173273605402</v>
+        <v>2.285031569608779</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
